--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484092_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484092_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1259</v>
+        <v>4.1749</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6687</v>
+        <v>2.8163</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5427999999999999</v>
+        <v>1.3586</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2818</v>
+        <v>3.114</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1098</v>
+        <v>1.2394</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.8279</v>
+        <v>1.8746</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6443</v>
+        <v>1.7374</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4837</v>
+        <v>0.0053</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1606</v>
+        <v>1.7321</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3625</v>
+        <v>1.3767</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3739</v>
+        <v>1.2341</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9886</v>
+        <v>0.1425</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0858</v>
+        <v>-0.5938</v>
       </c>
       <c r="T2" t="n">
-        <v>1.984</v>
+        <v>0.2098</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1018</v>
+        <v>-0.8035</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7502</v>
+        <v>0.266</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0162</v>
+        <v>0.8692</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1662</v>
+        <v>3.4255</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0601</v>
+        <v>4.5294</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1061</v>
+        <v>-1.1039</v>
       </c>
       <c r="G3" t="n">
-        <v>3.114</v>
+        <v>1.2818</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2394</v>
+        <v>3.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8746</v>
+        <v>-1.8279</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7374</v>
+        <v>3.6443</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0053</v>
+        <v>3.4837</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7321</v>
+        <v>0.1606</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3767</v>
+        <v>-2.3625</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2341</v>
+        <v>-0.3739</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1425</v>
+        <v>-1.9886</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6025</v>
+        <v>0.3854</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4535</v>
+        <v>0.8446</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.056</v>
+        <v>-0.4593</v>
       </c>
       <c r="V3" t="n">
-        <v>0.266</v>
+        <v>2.7502</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8692</v>
+        <v>3.0162</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2348</v>
+        <v>2.9739</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8401</v>
+        <v>2.8037</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3946</v>
+        <v>0.1702</v>
       </c>
       <c r="G4" t="n">
         <v>2.6541</v>
@@ -766,13 +766,13 @@
         <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4194</v>
+        <v>-0.6802</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9862</v>
+        <v>-0.0226</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4332</v>
+        <v>-0.6576</v>
       </c>
       <c r="V4" t="n">
         <v>0.6032</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7378</v>
+        <v>1.7746</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1854</v>
+        <v>-0.4291</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9232</v>
+        <v>2.2037</v>
       </c>
       <c r="G5" t="n">
         <v>1.5281</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5838</v>
+        <v>-0.547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4535</v>
+        <v>0.2098</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0373</v>
+        <v>-0.7568</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5737</v>
+        <v>1.669</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4398</v>
+        <v>3.1144</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8662</v>
+        <v>-1.4453</v>
       </c>
       <c r="G6" t="n">
         <v>1.8891</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.7916</v>
+        <v>-1.6962</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4137</v>
+        <v>0.2608</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.3779</v>
+        <v>-1.9571</v>
       </c>
       <c r="V6" t="n">
         <v>1.2777</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BOUSALEM GARZA</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1887</v>
+        <v>0.1461</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.647</v>
+        <v>-0.7006</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8357</v>
+        <v>0.8467</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2947</v>
+        <v>-1.5543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7456</v>
+        <v>-0.5191</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4508</v>
+        <v>-1.0351</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1408</v>
+        <v>-1.2491</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0605</v>
+        <v>0.0711</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0803</v>
+        <v>-1.3202</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1539</v>
+        <v>-0.3051</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6851</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5312</v>
+        <v>0.2851</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0267</v>
+        <v>-0.3033</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1133</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0867</v>
+        <v>-0.3713</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6745</v>
+        <v>1.0118</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6745</v>
+        <v>1.4724</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.4607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>I. BOUSALEM GARZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4031</v>
+        <v>-0.0015</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1937</v>
+        <v>-0.5847</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7906</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5543</v>
+        <v>0.2947</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5191</v>
+        <v>0.7456</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0351</v>
+        <v>-0.4508</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2491</v>
+        <v>0.1408</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0711</v>
+        <v>0.0605</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3202</v>
+        <v>0.0803</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3051</v>
+        <v>0.1539</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.6851</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2851</v>
+        <v>-0.5312</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8525</v>
+        <v>-0.2168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4251</v>
+        <v>-0.051</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4275</v>
+        <v>-0.1658</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0118</v>
+        <v>-0.6745</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4724</v>
+        <v>-0.6745</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7401</v>
+        <v>-0.383</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6139</v>
+        <v>-1.0805</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1261</v>
+        <v>0.6975</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5617</v>
+        <v>0.7682</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0707</v>
+        <v>0.1307</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.491</v>
+        <v>0.6375</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1006</v>
+        <v>1.2094</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0605</v>
+        <v>1.129</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>0.0803</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6623</v>
+        <v>-0.4412</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1312</v>
+        <v>-0.9983</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5312</v>
+        <v>0.5572</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3491</v>
+        <v>-0.4209</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0113</v>
+        <v>-0.306</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3378</v>
+        <v>-0.1149</v>
       </c>
       <c r="V9" t="n">
-        <v>0.266</v>
+        <v>-0.532</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0725</v>
+        <v>-0.8625</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5736</v>
+        <v>-0.5119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5011</v>
+        <v>-0.3506</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7682</v>
+        <v>-0.5617</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1307</v>
+        <v>-0.0707</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6375</v>
+        <v>-0.491</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2094</v>
+        <v>0.1006</v>
       </c>
       <c r="K10" t="n">
-        <v>1.129</v>
+        <v>0.0605</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0803</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4412</v>
+        <v>-0.6623</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9983</v>
+        <v>-0.1312</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5572</v>
+        <v>-0.5312</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1104</v>
+        <v>0.2267</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7991</v>
+        <v>0.1134</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3112</v>
+        <v>0.1133</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.532</v>
+        <v>0.266</v>
       </c>
       <c r="W10" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.532</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3329</v>
+        <v>-1.2207</v>
       </c>
       <c r="E11" t="n">
         <v>-0.8685</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4644</v>
+        <v>-0.3522</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0846</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2483</v>
+        <v>-0.136</v>
       </c>
       <c r="T11" t="n">
         <v>0.4932</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6292</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5102</v>
+        <v>-1.2398</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0832</v>
+        <v>0.0188</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4269</v>
+        <v>-1.2586</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6362</v>
@@ -1390,13 +1390,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1995</v>
+        <v>0.0709</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.6065</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.704</v>
+        <v>-0.5357</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6745</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4152</v>
+        <v>-2.6566</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2673</v>
+        <v>-2.2843</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1479</v>
+        <v>-0.3723</v>
       </c>
       <c r="G13" t="n">
         <v>2.5337</v>
@@ -1468,13 +1468,13 @@
         <v>2.579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1554</v>
+        <v>-0.3968</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1418</v>
+        <v>0.1248</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2972</v>
+        <v>-0.5216</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4129</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.553099999999999</v>
+        <v>7.7999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5761</v>
+        <v>6.823</v>
       </c>
       <c r="F14" t="n">
-        <v>0.977</v>
+        <v>0.9769999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>10.2269</v>
@@ -1516,7 +1516,7 @@
         <v>16.2514</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.024100000000001</v>
+        <v>-6.0241</v>
       </c>
       <c r="J14" t="n">
         <v>16.1644</v>
@@ -1531,7 +1531,7 @@
         <v>-5.9373</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1080999999999998</v>
+        <v>-0.1080999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-5.8294</v>
@@ -1546,13 +1546,13 @@
         <v>18.8465</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.555200000000001</v>
+        <v>-4.308</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3044</v>
+        <v>2.5514</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.8594</v>
+        <v>-6.859500000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.881</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7263</v>
+        <v>8.0313</v>
       </c>
       <c r="E15" t="n">
-        <v>8.224</v>
+        <v>8.8362</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4977</v>
+        <v>-0.8048</v>
       </c>
       <c r="G15" t="n">
         <v>6.3092</v>
@@ -1624,13 +1624,13 @@
         <v>3.3725</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7056</v>
+        <v>0.5995</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3232</v>
+        <v>0.9354</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0288</v>
+        <v>-0.3359</v>
       </c>
       <c r="V15" t="n">
         <v>-0.266</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2372</v>
+        <v>0.8357</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0165</v>
+        <v>3.1185</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7793</v>
+        <v>-2.2828</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8983</v>
@@ -1702,13 +1702,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4001</v>
+        <v>0.1984</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5726</v>
+        <v>0.6746</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9727</v>
+        <v>-0.4762</v>
       </c>
       <c r="V16" t="n">
         <v>0.9405</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.103</v>
+        <v>0.5937</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3725</v>
+        <v>-0.1551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2695</v>
+        <v>0.7488</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5791</v>
+        <v>-2.9897</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0881</v>
+        <v>-3.815</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.491</v>
+        <v>0.8253</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0528</v>
+        <v>-1.0831</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.093</v>
+        <v>-1.2087</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>0.1256</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5263</v>
+        <v>-1.9067</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0049</v>
+        <v>-2.6064</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5312</v>
+        <v>0.6997</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5952</v>
+        <v>2.9758</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5473</v>
+        <v>0.1786</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3467</v>
+        <v>0.4989</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2006</v>
+        <v>-0.3203</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6745</v>
+        <v>2.4129</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6745</v>
+        <v>2.4129</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7517</v>
+        <v>-1.1479</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4865</v>
+        <v>-1.0987</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2651</v>
+        <v>-0.0492</v>
       </c>
       <c r="G18" t="n">
         <v>0.5407999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>2.7774</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1756</v>
+        <v>0.7794</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3775</v>
+        <v>0.7653</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2019</v>
+        <v>0.0141</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2777</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8466</v>
+        <v>-1.4515</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3794</v>
+        <v>-1.801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.3494</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9897</v>
+        <v>-1.5791</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.815</v>
+        <v>-1.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8253</v>
+        <v>-0.491</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0831</v>
+        <v>-1.0528</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2087</v>
+        <v>-1.093</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1256</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9067</v>
+        <v>-0.5263</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.6064</v>
+        <v>0.0049</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6997</v>
+        <v>-0.5312</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9758</v>
+        <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2618</v>
+        <v>1.1989</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7254</v>
+        <v>0.9183</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5363</v>
+        <v>0.2806</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4129</v>
+        <v>-0.6745</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4129</v>
+        <v>-0.6745</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6036</v>
+        <v>-1.7127</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.874</v>
+        <v>-2.7259</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2703</v>
+        <v>1.0132</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2925</v>
+        <v>-2.2611</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.5831</v>
+        <v>-1.4915</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2906</v>
+        <v>-0.7696</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3089</v>
+        <v>-2.0004</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4375</v>
+        <v>-1.3604</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1286</v>
+        <v>-0.64</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9836</v>
+        <v>-0.2607</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.1456</v>
+        <v>-0.1312</v>
       </c>
       <c r="O20" t="n">
-        <v>0.162</v>
+        <v>-0.1295</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1903</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7774</v>
+        <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3472</v>
+        <v>0.4691</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8706</v>
+        <v>0.2664</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4766</v>
+        <v>0.2026</v>
       </c>
       <c r="V20" t="n">
-        <v>0.532</v>
+        <v>0.6745</v>
       </c>
       <c r="W20" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8309</v>
+        <v>-1.9222</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6239</v>
+        <v>-1.9694</v>
       </c>
       <c r="F21" t="n">
-        <v>0.793</v>
+        <v>0.0472</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2611</v>
+        <v>-3.5532</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4915</v>
+        <v>-2.3328</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7696</v>
+        <v>-1.2204</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0004</v>
+        <v>-2.2926</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3604</v>
+        <v>-1.7329</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.64</v>
+        <v>-0.5597</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2607</v>
+        <v>-1.2607</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1312</v>
+        <v>-0.6</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1295</v>
+        <v>-0.6607</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3509</v>
+        <v>0.8375</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3685</v>
+        <v>0.3231</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0176</v>
+        <v>0.5143</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.122</v>
+        <v>-2.3077</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1735</v>
+        <v>0.6251</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0515</v>
+        <v>-2.9329</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5532</v>
+        <v>-0.0781</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3328</v>
+        <v>-1.441</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2204</v>
+        <v>1.3629</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2926</v>
+        <v>1.1777</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7329</v>
+        <v>-0.7099</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5597</v>
+        <v>1.8876</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2607</v>
+        <v>-1.2558</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6</v>
+        <v>-0.7311</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6607</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6377</v>
+        <v>0.9254</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1191</v>
+        <v>0.7766</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.1488</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-3.3534</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6861</v>
+        <v>-2.6486</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5231</v>
+        <v>-2.6902</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2092</v>
+        <v>0.0417</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0781</v>
+        <v>-3.2925</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.441</v>
+        <v>-5.5831</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3629</v>
+        <v>2.2906</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1777</v>
+        <v>-0.3089</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7099</v>
+        <v>-2.4375</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8876</v>
+        <v>2.1286</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2558</v>
+        <v>-2.9836</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7311</v>
+        <v>-3.1456</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1903</v>
+        <v>2.7774</v>
       </c>
       <c r="S23" t="n">
-        <v>0.547</v>
+        <v>1.3023</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6746</v>
+        <v>1.0544</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1276</v>
+        <v>0.2479</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.3534</v>
+        <v>0.532</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3373</v>
+        <v>0.532</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.0162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5725</v>
+        <v>-2.7826</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8308</v>
+        <v>-3.1166</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2582</v>
+        <v>0.3339</v>
       </c>
       <c r="G24" t="n">
         <v>-2.425</v>
@@ -2326,13 +2326,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3168</v>
+        <v>1.1067</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0679</v>
+        <v>0.6463</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3848</v>
+        <v>0.4605</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8692</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.552899999999999</v>
+        <v>-4.512500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9769999999999981</v>
+        <v>-0.977100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.575999999999999</v>
+        <v>-3.5355</v>
       </c>
       <c r="G25" t="n">
         <v>-10.227</v>
@@ -2377,10 +2377,10 @@
         <v>6.0242</v>
       </c>
       <c r="J25" t="n">
-        <v>5.937299999999999</v>
+        <v>5.937300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1078999999999987</v>
+        <v>0.1078999999999993</v>
       </c>
       <c r="L25" t="n">
         <v>5.8294</v>
@@ -2392,7 +2392,7 @@
         <v>-16.3595</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1949</v>
+        <v>0.1948999999999998</v>
       </c>
       <c r="P25" t="n">
         <v>-9.999999999976694e-05</v>
@@ -2404,13 +2404,13 @@
         <v>18.8466</v>
       </c>
       <c r="S25" t="n">
-        <v>5.555</v>
+        <v>7.5958</v>
       </c>
       <c r="T25" t="n">
-        <v>6.859499999999999</v>
+        <v>6.8593</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3043</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8809</v>
